--- a/AAII_Financials/Quarterly/FRCOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRCOY_QTR_FIN.xlsx
@@ -2667,7 +2667,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>850500</v>
+        <v>1580000</v>
       </c>
       <c r="E58" s="3">
         <v>1349400</v>
@@ -2711,7 +2711,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2383000</v>
+        <v>1653500</v>
       </c>
       <c r="E59" s="3">
         <v>2620900</v>
@@ -2799,7 +2799,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3558500</v>
+        <v>2828900</v>
       </c>
       <c r="E61" s="3">
         <v>3583500</v>
@@ -2843,7 +2843,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>446000</v>
+        <v>1175500</v>
       </c>
       <c r="E62" s="3">
         <v>486400</v>
